--- a/UTCUTS/B1_Scenario_Config.xlsx
+++ b/UTCUTS/B1_Scenario_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yds3\Downloads\UTCUTS_20250218\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clgcr.sharepoint.com/sites/ClimateLeadGroup-NDC_Ecu/Documentos compartidos/ECU_NDC_model/lastest_models_2025_02_03/UTCUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C522958-69B0-40B2-B110-40E2BBD0356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3C522958-69B0-40B2-B110-40E2BBD0356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3385DB0-1A1E-448E-874D-94CD4D7C0586}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="705" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="11250" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="7" r:id="rId1"/>
@@ -1350,7 +1350,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
@@ -2612,61 +2612,61 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2683,48 +2683,45 @@
     </xf>
   </cellXfs>
   <cellStyles count="70">
-    <cellStyle name="20% - Accent1" xfId="44" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="48" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="52" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="56" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="60" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="64" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="45" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="49" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="53" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="57" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="61" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="65" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="46" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="50" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="54" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="58" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="62" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="66" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="43" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="47" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="51" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="55" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="59" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="63" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="32" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="36" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="38" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="44" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="48" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="52" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="56" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="60" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="64" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="45" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="49" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="53" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="57" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="61" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="65" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="46" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="50" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="54" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="58" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="62" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="66" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="31" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="36" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="38" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="37" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{8F6B87A3-B8F6-4AD8-A5CC-9E094647CFFD}"/>
-    <cellStyle name="Explanatory Text" xfId="41" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="31" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="27" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="28" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="29" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="30" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="27" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="30" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="43" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="47" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="51" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="55" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="59" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="63" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="34" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Hipervínculo 2" xfId="5" xr:uid="{66A34670-C63E-4E8F-985A-72A51D5F7F20}"/>
     <cellStyle name="Hipervínculo 2 2" xfId="8" xr:uid="{D6A4B84A-0E30-4711-AE96-39795C06189D}"/>
     <cellStyle name="Hipervínculo 2 3" xfId="17" xr:uid="{255FEE8A-D126-4801-838D-62A6F24B6117}"/>
     <cellStyle name="Hipervínculo 2 4" xfId="20" xr:uid="{B8245187-1651-4BE5-90D5-A9F3CEF796FC}"/>
     <cellStyle name="Hipervínculo 2 5" xfId="25" xr:uid="{74D7505F-E3C2-4938-A250-B3EDE02E4E2B}"/>
     <cellStyle name="Hyperlink 2" xfId="13" xr:uid="{52FE9B04-2383-43D1-8C5C-258E9B829945}"/>
-    <cellStyle name="Input" xfId="34" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="37" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Incorrecto" xfId="32" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Millares 2" xfId="12" xr:uid="{E91AFAE6-9D91-4526-9BD7-181E95D623CE}"/>
     <cellStyle name="Millares 2 2" xfId="1" xr:uid="{892390FE-96F8-4C48-BA57-C33D526789BF}"/>
     <cellStyle name="Neutral" xfId="33" builtinId="28" customBuiltin="1"/>
@@ -2747,12 +2744,15 @@
     <cellStyle name="Normal 3 7" xfId="21" xr:uid="{4448EB7D-10F3-4445-B1A8-9B60214EB158}"/>
     <cellStyle name="Normal 3 8" xfId="69" xr:uid="{ED03840A-A1D6-467F-8DAA-689E792731EA}"/>
     <cellStyle name="Normal 4" xfId="7" xr:uid="{704A5968-1437-408E-AA49-A36803776B62}"/>
-    <cellStyle name="Note" xfId="40" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="35" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="40" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Porcentaje 2" xfId="6" xr:uid="{CA224C2E-6FD6-41A7-B02B-44AF5C3F8AD1}"/>
-    <cellStyle name="Title" xfId="26" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="35" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="39" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="41" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="26" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="28" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="29" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="42" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="39" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3031,7 +3031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98ECE2FD-6781-40FC-9DD3-A79D8FD71BA2}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
@@ -3134,7 +3134,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AS1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
@@ -3300,7 +3300,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:BM1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.6640625" bestFit="1" customWidth="1"/>
@@ -3524,7 +3524,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:BM1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79.6640625" bestFit="1" customWidth="1"/>
@@ -3749,7 +3749,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:AB1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
@@ -3848,7 +3848,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1F0214-6FED-4AAE-89F9-1D5B4098AAFA}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
   </cols>
@@ -3881,7 +3881,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="41.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -3920,7 +3920,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
@@ -4003,7 +4003,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -4036,7 +4036,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" customWidth="1"/>
     <col min="2" max="2" width="39.6640625" customWidth="1"/>
@@ -4108,8 +4108,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE60582-8E84-4795-90E6-91E6C5CD9C07}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK378"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.6640625" style="20" customWidth="1"/>
     <col min="2" max="2" width="41.6640625" style="20" customWidth="1"/>
@@ -15660,7 +15661,7 @@
         <v>99.092504747186013</v>
       </c>
     </row>
-    <row r="115" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="63" t="s">
         <v>52</v>
       </c>
@@ -15761,7 +15762,7 @@
         <v>32.491510427267393</v>
       </c>
     </row>
-    <row r="116" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="63" t="s">
         <v>52</v>
       </c>
@@ -15862,7 +15863,7 @@
         <v>-0.36269996514052089</v>
       </c>
     </row>
-    <row r="117" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="63" t="s">
         <v>52</v>
       </c>
@@ -15963,7 +15964,7 @@
         <v>-1.0237139105904323</v>
       </c>
     </row>
-    <row r="118" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="63" t="s">
         <v>52</v>
       </c>
@@ -16064,7 +16065,7 @@
         <v>-3.5496667754924127</v>
       </c>
     </row>
-    <row r="119" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="63" t="s">
         <v>52</v>
       </c>
@@ -16165,7 +16166,7 @@
         <v>-0.26463245644416616</v>
       </c>
     </row>
-    <row r="120" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="63" t="s">
         <v>52</v>
       </c>
@@ -16266,7 +16267,7 @@
         <v>-5.9683784487227634</v>
       </c>
     </row>
-    <row r="121" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="63" t="s">
         <v>52</v>
       </c>
@@ -16367,7 +16368,7 @@
         <v>-5.1291027710195118</v>
       </c>
     </row>
-    <row r="122" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="63" t="s">
         <v>52</v>
       </c>
@@ -16468,7 +16469,7 @@
         <v>-6.6244933333333336</v>
       </c>
     </row>
-    <row r="123" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="63" t="s">
         <v>52</v>
       </c>
@@ -16569,7 +16570,7 @@
         <v>-6.5223015693940791</v>
       </c>
     </row>
-    <row r="124" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="63" t="s">
         <v>52</v>
       </c>
@@ -16670,7 +16671,7 @@
         <v>67.848462946402847</v>
       </c>
     </row>
-    <row r="125" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="66" t="s">
         <v>52</v>
       </c>
@@ -16771,7 +16772,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="126" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="66" t="s">
         <v>52</v>
       </c>
@@ -16872,7 +16873,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="127" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="66" t="s">
         <v>52</v>
       </c>
@@ -16973,7 +16974,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="128" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="66" t="s">
         <v>52</v>
       </c>
@@ -17074,7 +17075,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="129" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="66" t="s">
         <v>52</v>
       </c>
@@ -17175,7 +17176,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="130" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="66" t="s">
         <v>52</v>
       </c>
@@ -17276,7 +17277,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="131" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="66" t="s">
         <v>52</v>
       </c>
@@ -17377,7 +17378,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="132" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="66" t="s">
         <v>52</v>
       </c>
@@ -17478,7 +17479,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="133" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="66" t="s">
         <v>52</v>
       </c>
@@ -17579,7 +17580,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="134" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="66" t="s">
         <v>52</v>
       </c>
@@ -17680,7 +17681,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="135" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="63" t="s">
         <v>52</v>
       </c>
@@ -17781,7 +17782,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="136" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="63" t="s">
         <v>52</v>
       </c>
@@ -17882,7 +17883,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="137" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="63" t="s">
         <v>52</v>
       </c>
@@ -17983,7 +17984,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="138" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="63" t="s">
         <v>52</v>
       </c>
@@ -18084,7 +18085,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="139" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="63" t="s">
         <v>52</v>
       </c>
@@ -18185,7 +18186,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="140" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="63" t="s">
         <v>52</v>
       </c>
@@ -18286,7 +18287,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="141" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="63" t="s">
         <v>52</v>
       </c>
@@ -18387,7 +18388,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="142" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="63" t="s">
         <v>52</v>
       </c>
@@ -18488,7 +18489,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="143" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="63" t="s">
         <v>52</v>
       </c>
@@ -18589,7 +18590,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="144" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="63" t="s">
         <v>52</v>
       </c>
@@ -18690,7 +18691,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="145" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="66" t="s">
         <v>52</v>
       </c>
@@ -18791,7 +18792,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="146" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="66" t="s">
         <v>52</v>
       </c>
@@ -18892,7 +18893,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="147" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="66" t="s">
         <v>52</v>
       </c>
@@ -18993,7 +18994,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="148" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="66" t="s">
         <v>52</v>
       </c>
@@ -19094,7 +19095,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="149" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="66" t="s">
         <v>52</v>
       </c>
@@ -19195,7 +19196,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="150" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="66" t="s">
         <v>52</v>
       </c>
@@ -19296,7 +19297,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="151" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="66" t="s">
         <v>52</v>
       </c>
@@ -19397,7 +19398,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="152" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="66" t="s">
         <v>52</v>
       </c>
@@ -19498,7 +19499,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="153" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="66" t="s">
         <v>52</v>
       </c>
@@ -19599,7 +19600,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="154" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="66" t="s">
         <v>52</v>
       </c>
@@ -19700,7 +19701,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="155" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="63" t="s">
         <v>52</v>
       </c>
@@ -19801,7 +19802,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="156" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="63" t="s">
         <v>52</v>
       </c>
@@ -19902,7 +19903,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="157" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="63" t="s">
         <v>52</v>
       </c>
@@ -20003,7 +20004,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="158" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="63" t="s">
         <v>52</v>
       </c>
@@ -20104,7 +20105,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="159" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="63" t="s">
         <v>52</v>
       </c>
@@ -20205,7 +20206,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="160" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="63" t="s">
         <v>52</v>
       </c>
@@ -20306,7 +20307,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="161" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="63" t="s">
         <v>52</v>
       </c>
@@ -20407,7 +20408,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="162" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="63" t="s">
         <v>52</v>
       </c>
@@ -20508,7 +20509,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="163" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="63" t="s">
         <v>52</v>
       </c>
@@ -20609,7 +20610,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="164" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="63" t="s">
         <v>52</v>
       </c>
@@ -20710,7 +20711,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="165" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="66" t="s">
         <v>52</v>
       </c>
@@ -20811,7 +20812,7 @@
         <v>42.860489191335063</v>
       </c>
     </row>
-    <row r="166" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="66" t="s">
         <v>52</v>
       </c>
@@ -20912,7 +20913,7 @@
         <v>63.419628531405088</v>
       </c>
     </row>
-    <row r="167" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="66" t="s">
         <v>52</v>
       </c>
@@ -21013,7 +21014,7 @@
         <v>626.230106991909</v>
       </c>
     </row>
-    <row r="168" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="66" t="s">
         <v>52</v>
       </c>
@@ -21114,7 +21115,7 @@
         <v>235.96930024970101</v>
       </c>
     </row>
-    <row r="169" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="66" t="s">
         <v>52</v>
       </c>
@@ -21215,7 +21216,7 @@
         <v>924.56987481668943</v>
       </c>
     </row>
-    <row r="170" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="66" t="s">
         <v>52</v>
       </c>
@@ -21316,7 +21317,7 @@
         <v>697.76825439679851</v>
       </c>
     </row>
-    <row r="171" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="66" t="s">
         <v>52</v>
       </c>
@@ -21417,7 +21418,7 @@
         <v>82.55943237168384</v>
       </c>
     </row>
-    <row r="172" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="66" t="s">
         <v>52</v>
       </c>
@@ -21518,7 +21519,7 @@
         <v>1383.3222804556538</v>
       </c>
     </row>
-    <row r="173" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="66" t="s">
         <v>52</v>
       </c>
@@ -21619,7 +21620,7 @@
         <v>3603.1537451666527</v>
       </c>
     </row>
-    <row r="174" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="66" t="s">
         <v>52</v>
       </c>
@@ -21720,7 +21721,7 @@
         <v>124.52641059098268</v>
       </c>
     </row>
-    <row r="175" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="63" t="s">
         <v>52</v>
       </c>
@@ -21821,7 +21822,7 @@
         <v>99.486395671910685</v>
       </c>
     </row>
-    <row r="176" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="63" t="s">
         <v>52</v>
       </c>
@@ -21922,7 +21923,7 @@
         <v>-11.916666666666666</v>
       </c>
     </row>
-    <row r="177" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="63" t="s">
         <v>52</v>
       </c>
@@ -22023,7 +22024,7 @@
         <v>-1.8333333333333333</v>
       </c>
     </row>
-    <row r="178" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="63" t="s">
         <v>52</v>
       </c>
@@ -22124,7 +22125,7 @@
         <v>-11.916666666666666</v>
       </c>
     </row>
-    <row r="179" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="66" t="s">
         <v>52</v>
       </c>
@@ -22225,7 +22226,7 @@
         <v>64.10882495769107</v>
       </c>
     </row>
-    <row r="180" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="66" t="s">
         <v>52</v>
       </c>
@@ -22326,7 +22327,7 @@
         <v>30.229043839100068</v>
       </c>
     </row>
-    <row r="181" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="66" t="s">
         <v>52</v>
       </c>
@@ -22427,7 +22428,7 @@
         <v>173.36699916070251</v>
       </c>
     </row>
-    <row r="182" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="66" t="s">
         <v>52</v>
       </c>
@@ -22528,7 +22529,7 @@
         <v>347.1533952409888</v>
       </c>
     </row>
-    <row r="183" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="66" t="s">
         <v>52</v>
       </c>
@@ -22629,7 +22630,7 @@
         <v>67.997143884375589</v>
       </c>
     </row>
-    <row r="184" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="66" t="s">
         <v>52</v>
       </c>
@@ -22730,7 +22731,7 @@
         <v>2029.1847911983693</v>
       </c>
     </row>
-    <row r="185" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="66" t="s">
         <v>52</v>
       </c>
@@ -22831,7 +22832,7 @@
         <v>74.531431079523387</v>
       </c>
     </row>
-    <row r="186" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="66" t="s">
         <v>52</v>
       </c>
@@ -22932,7 +22933,7 @@
         <v>80.044311779586664</v>
       </c>
     </row>
-    <row r="187" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="66" t="s">
         <v>52</v>
       </c>
@@ -23033,7 +23034,7 @@
         <v>6442.3018078818859</v>
       </c>
     </row>
-    <row r="188" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="66" t="s">
         <v>52</v>
       </c>
@@ -23134,7 +23135,7 @@
         <v>15.070253307070301</v>
       </c>
     </row>
-    <row r="189" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="66" t="s">
         <v>52</v>
       </c>
@@ -23235,7 +23236,7 @@
         <v>105.44970700730272</v>
       </c>
     </row>
-    <row r="190" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="66" t="s">
         <v>52</v>
       </c>
@@ -23336,7 +23337,7 @@
         <v>-6.2732153227034972</v>
       </c>
     </row>
-    <row r="191" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="66" t="s">
         <v>52</v>
       </c>
@@ -23437,7 +23438,7 @@
         <v>-6.7293404248102737</v>
       </c>
     </row>
-    <row r="192" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="63" t="s">
         <v>52</v>
       </c>
@@ -23538,7 +23539,7 @@
         <v>8.7333175741121316E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="63" t="s">
         <v>52</v>
       </c>
@@ -23639,7 +23640,7 @@
         <v>0.40095983346994529</v>
       </c>
     </row>
-    <row r="194" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="63" t="s">
         <v>52</v>
       </c>
@@ -23740,7 +23741,7 @@
         <v>0.15990831319010956</v>
       </c>
     </row>
-    <row r="195" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="63" t="s">
         <v>52</v>
       </c>
@@ -23841,7 +23842,7 @@
         <v>3.1712780227642158E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="63" t="s">
         <v>52</v>
       </c>
@@ -23942,7 +23943,7 @@
         <v>0.85867594587155094</v>
       </c>
     </row>
-    <row r="197" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="63" t="s">
         <v>52</v>
       </c>
@@ -24043,7 +24044,7 @@
         <v>3.3083247291850838E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="63" t="s">
         <v>52</v>
       </c>
@@ -24144,7 +24145,7 @@
         <v>0.20304440764049608</v>
       </c>
     </row>
-    <row r="199" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="63" t="s">
         <v>52</v>
       </c>
@@ -24245,7 +24246,7 @@
         <v>0.11919219637550635</v>
       </c>
     </row>
-    <row r="200" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="63" t="s">
         <v>52</v>
       </c>
@@ -24346,7 +24347,7 @@
         <v>6.8040626640608615E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="63" t="s">
         <v>52</v>
       </c>
@@ -24447,7 +24448,7 @@
         <v>0.93575920557287939</v>
       </c>
     </row>
-    <row r="202" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="63" t="s">
         <v>52</v>
       </c>
@@ -24548,7 +24549,7 @@
         <v>64.82622298373164</v>
       </c>
     </row>
-    <row r="203" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="63" t="s">
         <v>52</v>
       </c>
@@ -24649,7 +24650,7 @@
         <v>16.183561425046342</v>
       </c>
     </row>
-    <row r="204" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="66" t="s">
         <v>52</v>
       </c>
@@ -24750,7 +24751,7 @@
         <v>149.38158738990609</v>
       </c>
     </row>
-    <row r="205" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="66" t="s">
         <v>52</v>
       </c>
@@ -24851,7 +24852,7 @@
         <v>30.461662171067022</v>
       </c>
     </row>
-    <row r="206" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="66" t="s">
         <v>52</v>
       </c>
@@ -24952,7 +24953,7 @@
         <v>1301.9986066670313</v>
       </c>
     </row>
-    <row r="207" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="66" t="s">
         <v>52</v>
       </c>
@@ -25053,7 +25054,7 @@
         <v>428.31166871896397</v>
       </c>
     </row>
-    <row r="208" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="66" t="s">
         <v>52</v>
       </c>
@@ -25154,7 +25155,7 @@
         <v>15480.433027335732</v>
       </c>
     </row>
-    <row r="209" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="66" t="s">
         <v>52</v>
       </c>
@@ -25255,7 +25256,7 @@
         <v>877.87843458467682</v>
       </c>
     </row>
-    <row r="210" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="66" t="s">
         <v>52</v>
       </c>
@@ -25356,7 +25357,7 @@
         <v>479.43810229203001</v>
       </c>
     </row>
-    <row r="211" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="66" t="s">
         <v>52</v>
       </c>
@@ -25457,7 +25458,7 @@
         <v>104.4106349195834</v>
       </c>
     </row>
-    <row r="212" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="66" t="s">
         <v>52</v>
       </c>
@@ -25558,7 +25559,7 @@
         <v>4373.535396592134</v>
       </c>
     </row>
-    <row r="213" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="66" t="s">
         <v>52</v>
       </c>
@@ -25659,7 +25660,7 @@
         <v>307.4837785193746</v>
       </c>
     </row>
-    <row r="214" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="66" t="s">
         <v>52</v>
       </c>
@@ -25760,7 +25761,7 @@
         <v>238.33333333333334</v>
       </c>
     </row>
-    <row r="215" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="66" t="s">
         <v>52</v>
       </c>
@@ -25861,7 +25862,7 @@
         <v>127.7040586000216</v>
       </c>
     </row>
-    <row r="216" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="63" t="s">
         <v>52</v>
       </c>
@@ -25962,7 +25963,7 @@
         <v>592.95687067658605</v>
       </c>
     </row>
-    <row r="217" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="63" t="s">
         <v>52</v>
       </c>
@@ -26063,7 +26064,7 @@
         <v>91.89969013080362</v>
       </c>
     </row>
-    <row r="218" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="63" t="s">
         <v>52</v>
       </c>
@@ -26164,7 +26165,7 @@
         <v>694.15506547743462</v>
       </c>
     </row>
-    <row r="219" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="63" t="s">
         <v>52</v>
       </c>
@@ -26265,7 +26266,7 @@
         <v>676.33523627579405</v>
       </c>
     </row>
-    <row r="220" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="63" t="s">
         <v>52</v>
       </c>
@@ -26366,7 +26367,7 @@
         <v>406.41047111214317</v>
       </c>
     </row>
-    <row r="221" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="63" t="s">
         <v>52</v>
       </c>
@@ -26467,7 +26468,7 @@
         <v>943.66267108859415</v>
       </c>
     </row>
-    <row r="222" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="63" t="s">
         <v>52</v>
       </c>
@@ -26568,7 +26569,7 @@
         <v>748.20703900868182</v>
       </c>
     </row>
-    <row r="223" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="63" t="s">
         <v>52</v>
       </c>
@@ -26669,7 +26670,7 @@
         <v>52.459117407483411</v>
       </c>
     </row>
-    <row r="224" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="63" t="s">
         <v>52</v>
       </c>
@@ -26770,7 +26771,7 @@
         <v>4340.5112813314909</v>
       </c>
     </row>
-    <row r="225" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="63" t="s">
         <v>52</v>
       </c>
@@ -26871,7 +26872,7 @@
         <v>285.54932122857923</v>
       </c>
     </row>
-    <row r="226" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="63" t="s">
         <v>52</v>
       </c>
@@ -26972,7 +26973,7 @@
         <v>238.33333333333334</v>
       </c>
     </row>
-    <row r="227" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="63" t="s">
         <v>52</v>
       </c>
@@ -27073,7 +27074,7 @@
         <v>99.092504747186013</v>
       </c>
     </row>
-    <row r="228" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="63" t="s">
         <v>56</v>
       </c>
@@ -27174,7 +27175,7 @@
         <v>32.491510427267393</v>
       </c>
     </row>
-    <row r="229" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="63" t="s">
         <v>56</v>
       </c>
@@ -27275,7 +27276,7 @@
         <v>-0.36269996514052089</v>
       </c>
     </row>
-    <row r="230" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="63" t="s">
         <v>56</v>
       </c>
@@ -27376,7 +27377,7 @@
         <v>-1.0237139105904323</v>
       </c>
     </row>
-    <row r="231" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="63" t="s">
         <v>56</v>
       </c>
@@ -27477,7 +27478,7 @@
         <v>-3.5496667754924127</v>
       </c>
     </row>
-    <row r="232" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="63" t="s">
         <v>56</v>
       </c>
@@ -27578,7 +27579,7 @@
         <v>-0.26463245644416616</v>
       </c>
     </row>
-    <row r="233" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="63" t="s">
         <v>56</v>
       </c>
@@ -27679,7 +27680,7 @@
         <v>-5.9683784487227634</v>
       </c>
     </row>
-    <row r="234" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="63" t="s">
         <v>56</v>
       </c>
@@ -27780,7 +27781,7 @@
         <v>-5.1291027710195118</v>
       </c>
     </row>
-    <row r="235" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="63" t="s">
         <v>56</v>
       </c>
@@ -27881,7 +27882,7 @@
         <v>-6.6244933333333336</v>
       </c>
     </row>
-    <row r="236" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="63" t="s">
         <v>56</v>
       </c>
@@ -27982,7 +27983,7 @@
         <v>-6.5223015693940791</v>
       </c>
     </row>
-    <row r="237" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="63" t="s">
         <v>56</v>
       </c>
@@ -28083,7 +28084,7 @@
         <v>67.848462946402847</v>
       </c>
     </row>
-    <row r="238" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="66" t="s">
         <v>56</v>
       </c>
@@ -28184,7 +28185,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="239" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="66" t="s">
         <v>56</v>
       </c>
@@ -28285,7 +28286,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="240" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="66" t="s">
         <v>56</v>
       </c>
@@ -28386,7 +28387,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="241" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="66" t="s">
         <v>56</v>
       </c>
@@ -28487,7 +28488,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="242" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="66" t="s">
         <v>56</v>
       </c>
@@ -28588,7 +28589,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="243" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="66" t="s">
         <v>56</v>
       </c>
@@ -28689,7 +28690,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="244" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="66" t="s">
         <v>56</v>
       </c>
@@ -28790,7 +28791,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="245" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="66" t="s">
         <v>56</v>
       </c>
@@ -28891,7 +28892,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="246" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="66" t="s">
         <v>56</v>
       </c>
@@ -28992,7 +28993,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="247" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="66" t="s">
         <v>56</v>
       </c>
@@ -29093,7 +29094,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="248" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="63" t="s">
         <v>56</v>
       </c>
@@ -29194,7 +29195,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="249" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="63" t="s">
         <v>56</v>
       </c>
@@ -29295,7 +29296,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="250" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="63" t="s">
         <v>56</v>
       </c>
@@ -29396,7 +29397,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="251" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="63" t="s">
         <v>56</v>
       </c>
@@ -29497,7 +29498,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="252" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="63" t="s">
         <v>56</v>
       </c>
@@ -29598,7 +29599,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="253" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="63" t="s">
         <v>56</v>
       </c>
@@ -29699,7 +29700,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="254" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="63" t="s">
         <v>56</v>
       </c>
@@ -29800,7 +29801,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="255" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="63" t="s">
         <v>56</v>
       </c>
@@ -29901,7 +29902,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="256" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="63" t="s">
         <v>56</v>
       </c>
@@ -30002,7 +30003,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="257" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="63" t="s">
         <v>56</v>
       </c>
@@ -30103,7 +30104,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="258" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="66" t="s">
         <v>56</v>
       </c>
@@ -30204,7 +30205,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="259" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="66" t="s">
         <v>56</v>
       </c>
@@ -30305,7 +30306,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="260" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="66" t="s">
         <v>56</v>
       </c>
@@ -30406,7 +30407,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="261" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="66" t="s">
         <v>56</v>
       </c>
@@ -30507,7 +30508,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="262" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="66" t="s">
         <v>56</v>
       </c>
@@ -30608,7 +30609,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="263" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="66" t="s">
         <v>56</v>
       </c>
@@ -30709,7 +30710,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="264" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="66" t="s">
         <v>56</v>
       </c>
@@ -30810,7 +30811,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="265" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="66" t="s">
         <v>56</v>
       </c>
@@ -30911,7 +30912,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="266" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="66" t="s">
         <v>56</v>
       </c>
@@ -31012,7 +31013,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="267" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="66" t="s">
         <v>56</v>
       </c>
@@ -31113,7 +31114,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="268" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="63" t="s">
         <v>56</v>
       </c>
@@ -31214,7 +31215,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="269" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="63" t="s">
         <v>56</v>
       </c>
@@ -31315,7 +31316,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="270" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="63" t="s">
         <v>56</v>
       </c>
@@ -31416,7 +31417,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="271" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="63" t="s">
         <v>56</v>
       </c>
@@ -31517,7 +31518,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="272" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="63" t="s">
         <v>56</v>
       </c>
@@ -31618,7 +31619,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="273" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="63" t="s">
         <v>56</v>
       </c>
@@ -31719,7 +31720,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="274" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="63" t="s">
         <v>56</v>
       </c>
@@ -31820,7 +31821,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="275" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="63" t="s">
         <v>56</v>
       </c>
@@ -31921,7 +31922,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="276" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="63" t="s">
         <v>56</v>
       </c>
@@ -32022,7 +32023,7 @@
         <v>-21.198191666666666</v>
       </c>
     </row>
-    <row r="277" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="63" t="s">
         <v>56</v>
       </c>
@@ -32123,7 +32124,7 @@
         <v>-21.198191666666663</v>
       </c>
     </row>
-    <row r="278" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="66" t="s">
         <v>56</v>
       </c>
@@ -32224,7 +32225,7 @@
         <v>42.860489191335063</v>
       </c>
     </row>
-    <row r="279" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="66" t="s">
         <v>56</v>
       </c>
@@ -32325,7 +32326,7 @@
         <v>63.419628531405088</v>
       </c>
     </row>
-    <row r="280" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="66" t="s">
         <v>56</v>
       </c>
@@ -32426,7 +32427,7 @@
         <v>626.230106991909</v>
       </c>
     </row>
-    <row r="281" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="66" t="s">
         <v>56</v>
       </c>
@@ -32527,7 +32528,7 @@
         <v>235.96930024970101</v>
       </c>
     </row>
-    <row r="282" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="66" t="s">
         <v>56</v>
       </c>
@@ -32628,7 +32629,7 @@
         <v>924.56987481668943</v>
       </c>
     </row>
-    <row r="283" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="66" t="s">
         <v>56</v>
       </c>
@@ -32729,7 +32730,7 @@
         <v>697.76825439679851</v>
       </c>
     </row>
-    <row r="284" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="66" t="s">
         <v>56</v>
       </c>
@@ -32830,7 +32831,7 @@
         <v>82.55943237168384</v>
       </c>
     </row>
-    <row r="285" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="66" t="s">
         <v>56</v>
       </c>
@@ -32931,7 +32932,7 @@
         <v>1383.3222804556538</v>
       </c>
     </row>
-    <row r="286" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="66" t="s">
         <v>56</v>
       </c>
@@ -33032,7 +33033,7 @@
         <v>3603.1537451666527</v>
       </c>
     </row>
-    <row r="287" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="66" t="s">
         <v>56</v>
       </c>
@@ -33133,7 +33134,7 @@
         <v>124.52641059098268</v>
       </c>
     </row>
-    <row r="288" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="63" t="s">
         <v>56</v>
       </c>
@@ -33234,7 +33235,7 @@
         <v>99.486395671910685</v>
       </c>
     </row>
-    <row r="289" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="63" t="s">
         <v>56</v>
       </c>
@@ -33335,7 +33336,7 @@
         <v>-11.916666666666666</v>
       </c>
     </row>
-    <row r="290" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="63" t="s">
         <v>56</v>
       </c>
@@ -33436,7 +33437,7 @@
         <v>-1.8333333333333333</v>
       </c>
     </row>
-    <row r="291" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="63" t="s">
         <v>56</v>
       </c>
@@ -33537,7 +33538,7 @@
         <v>-11.916666666666666</v>
       </c>
     </row>
-    <row r="292" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="66" t="s">
         <v>56</v>
       </c>
@@ -33638,7 +33639,7 @@
         <v>64.10882495769107</v>
       </c>
     </row>
-    <row r="293" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="66" t="s">
         <v>56</v>
       </c>
@@ -33739,7 +33740,7 @@
         <v>30.229043839100068</v>
       </c>
     </row>
-    <row r="294" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="66" t="s">
         <v>56</v>
       </c>
@@ -33840,7 +33841,7 @@
         <v>173.36699916070251</v>
       </c>
     </row>
-    <row r="295" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="66" t="s">
         <v>56</v>
       </c>
@@ -33941,7 +33942,7 @@
         <v>347.1533952409888</v>
       </c>
     </row>
-    <row r="296" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="66" t="s">
         <v>56</v>
       </c>
@@ -34042,7 +34043,7 @@
         <v>67.997143884375589</v>
       </c>
     </row>
-    <row r="297" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="66" t="s">
         <v>56</v>
       </c>
@@ -34143,7 +34144,7 @@
         <v>2029.1847911983693</v>
       </c>
     </row>
-    <row r="298" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="66" t="s">
         <v>56</v>
       </c>
@@ -34244,7 +34245,7 @@
         <v>74.531431079523387</v>
       </c>
     </row>
-    <row r="299" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="66" t="s">
         <v>56</v>
       </c>
@@ -34345,7 +34346,7 @@
         <v>80.044311779586664</v>
       </c>
     </row>
-    <row r="300" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="66" t="s">
         <v>56</v>
       </c>
@@ -34446,7 +34447,7 @@
         <v>6442.3018078818859</v>
       </c>
     </row>
-    <row r="301" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="66" t="s">
         <v>56</v>
       </c>
@@ -34547,7 +34548,7 @@
         <v>15.070253307070301</v>
       </c>
     </row>
-    <row r="302" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="66" t="s">
         <v>56</v>
       </c>
@@ -34648,7 +34649,7 @@
         <v>105.44970700730272</v>
       </c>
     </row>
-    <row r="303" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="66" t="s">
         <v>56</v>
       </c>
@@ -34749,7 +34750,7 @@
         <v>-6.2732153227034972</v>
       </c>
     </row>
-    <row r="304" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="66" t="s">
         <v>56</v>
       </c>
@@ -34850,7 +34851,7 @@
         <v>-6.7293404248102737</v>
       </c>
     </row>
-    <row r="305" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="63" t="s">
         <v>56</v>
       </c>
@@ -34951,7 +34952,7 @@
         <v>8.7333175741121316E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="63" t="s">
         <v>56</v>
       </c>
@@ -35052,7 +35053,7 @@
         <v>0.40095983346994529</v>
       </c>
     </row>
-    <row r="307" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="63" t="s">
         <v>56</v>
       </c>
@@ -35153,7 +35154,7 @@
         <v>0.15990831319010956</v>
       </c>
     </row>
-    <row r="308" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="63" t="s">
         <v>56</v>
       </c>
@@ -35254,7 +35255,7 @@
         <v>3.1712780227642158E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="63" t="s">
         <v>56</v>
       </c>
@@ -35355,7 +35356,7 @@
         <v>0.85867594587155094</v>
       </c>
     </row>
-    <row r="310" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="63" t="s">
         <v>56</v>
       </c>
@@ -35456,7 +35457,7 @@
         <v>3.3083247291850838E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="63" t="s">
         <v>56</v>
       </c>
@@ -35557,7 +35558,7 @@
         <v>0.20304440764049608</v>
       </c>
     </row>
-    <row r="312" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="63" t="s">
         <v>56</v>
       </c>
@@ -35658,7 +35659,7 @@
         <v>0.11919219637550635</v>
       </c>
     </row>
-    <row r="313" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="63" t="s">
         <v>56</v>
       </c>
@@ -35759,7 +35760,7 @@
         <v>6.8040626640608615E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="63" t="s">
         <v>56</v>
       </c>
@@ -35860,7 +35861,7 @@
         <v>0.93575920557287939</v>
       </c>
     </row>
-    <row r="315" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="63" t="s">
         <v>56</v>
       </c>
@@ -35961,7 +35962,7 @@
         <v>64.82622298373164</v>
       </c>
     </row>
-    <row r="316" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="63" t="s">
         <v>56</v>
       </c>
@@ -36062,7 +36063,7 @@
         <v>16.183561425046342</v>
       </c>
     </row>
-    <row r="317" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="66" t="s">
         <v>56</v>
       </c>
@@ -36163,7 +36164,7 @@
         <v>149.38158738990609</v>
       </c>
     </row>
-    <row r="318" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="66" t="s">
         <v>56</v>
       </c>
@@ -36264,7 +36265,7 @@
         <v>30.461662171067022</v>
       </c>
     </row>
-    <row r="319" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="66" t="s">
         <v>56</v>
       </c>
@@ -36365,7 +36366,7 @@
         <v>1301.9986066670313</v>
       </c>
     </row>
-    <row r="320" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="66" t="s">
         <v>56</v>
       </c>
@@ -36466,7 +36467,7 @@
         <v>428.31166871896397</v>
       </c>
     </row>
-    <row r="321" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="66" t="s">
         <v>56</v>
       </c>
@@ -36567,7 +36568,7 @@
         <v>15480.433027335732</v>
       </c>
     </row>
-    <row r="322" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="66" t="s">
         <v>56</v>
       </c>
@@ -36668,7 +36669,7 @@
         <v>877.87843458467682</v>
       </c>
     </row>
-    <row r="323" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="66" t="s">
         <v>56</v>
       </c>
@@ -36769,7 +36770,7 @@
         <v>479.43810229203001</v>
       </c>
     </row>
-    <row r="324" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="66" t="s">
         <v>56</v>
       </c>
@@ -36870,7 +36871,7 @@
         <v>104.4106349195834</v>
       </c>
     </row>
-    <row r="325" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="66" t="s">
         <v>56</v>
       </c>
@@ -36971,7 +36972,7 @@
         <v>4373.535396592134</v>
       </c>
     </row>
-    <row r="326" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="66" t="s">
         <v>56</v>
       </c>
@@ -37072,7 +37073,7 @@
         <v>307.4837785193746</v>
       </c>
     </row>
-    <row r="327" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="66" t="s">
         <v>56</v>
       </c>
@@ -37173,7 +37174,7 @@
         <v>238.33333333333334</v>
       </c>
     </row>
-    <row r="328" spans="1:37" s="66" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:37" s="66" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="66" t="s">
         <v>56</v>
       </c>
@@ -37274,7 +37275,7 @@
         <v>127.7040586000216</v>
       </c>
     </row>
-    <row r="329" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="63" t="s">
         <v>56</v>
       </c>
@@ -37375,7 +37376,7 @@
         <v>592.95687067658605</v>
       </c>
     </row>
-    <row r="330" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="63" t="s">
         <v>56</v>
       </c>
@@ -37476,7 +37477,7 @@
         <v>91.89969013080362</v>
       </c>
     </row>
-    <row r="331" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="63" t="s">
         <v>56</v>
       </c>
@@ -37577,7 +37578,7 @@
         <v>694.15506547743462</v>
       </c>
     </row>
-    <row r="332" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="63" t="s">
         <v>56</v>
       </c>
@@ -37678,7 +37679,7 @@
         <v>676.33523627579405</v>
       </c>
     </row>
-    <row r="333" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="63" t="s">
         <v>56</v>
       </c>
@@ -37779,7 +37780,7 @@
         <v>406.41047111214317</v>
       </c>
     </row>
-    <row r="334" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="63" t="s">
         <v>56</v>
       </c>
@@ -37880,7 +37881,7 @@
         <v>943.66267108859415</v>
       </c>
     </row>
-    <row r="335" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="63" t="s">
         <v>56</v>
       </c>
@@ -37981,7 +37982,7 @@
         <v>748.20703900868182</v>
       </c>
     </row>
-    <row r="336" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="63" t="s">
         <v>56</v>
       </c>
@@ -38082,7 +38083,7 @@
         <v>52.459117407483411</v>
       </c>
     </row>
-    <row r="337" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="63" t="s">
         <v>56</v>
       </c>
@@ -38183,7 +38184,7 @@
         <v>4340.5112813314909</v>
       </c>
     </row>
-    <row r="338" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="63" t="s">
         <v>56</v>
       </c>
@@ -38284,7 +38285,7 @@
         <v>285.54932122857923</v>
       </c>
     </row>
-    <row r="339" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="63" t="s">
         <v>56</v>
       </c>
@@ -38385,7 +38386,7 @@
         <v>238.33333333333334</v>
       </c>
     </row>
-    <row r="340" spans="1:37" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:37" s="63" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="63" t="s">
         <v>56</v>
       </c>
@@ -38486,7 +38487,7 @@
         <v>99.092504747186013</v>
       </c>
     </row>
-    <row r="341" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="63" t="s">
         <v>56</v>
       </c>
@@ -38588,7 +38589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="63" t="s">
         <v>56</v>
       </c>
@@ -38690,7 +38691,7 @@
         <v>-0.348826968229209</v>
       </c>
     </row>
-    <row r="343" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="63" t="s">
         <v>56</v>
       </c>
@@ -38792,7 +38793,7 @@
         <v>-6.6244933333333318</v>
       </c>
     </row>
-    <row r="344" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="63" t="s">
         <v>56</v>
       </c>
@@ -38894,7 +38895,7 @@
         <v>-6.624493089772062</v>
       </c>
     </row>
-    <row r="345" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="63" t="s">
         <v>56</v>
       </c>
@@ -38996,7 +38997,7 @@
         <v>-6.6183763185535867</v>
       </c>
     </row>
-    <row r="346" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="63" t="s">
         <v>56</v>
       </c>
@@ -39098,7 +39099,7 @@
         <v>-6.6246377848340252</v>
       </c>
     </row>
-    <row r="347" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="63" t="s">
         <v>56</v>
       </c>
@@ -39200,7 +39201,7 @@
         <v>-2.9917055669930508</v>
       </c>
     </row>
-    <row r="348" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="63" t="s">
         <v>56</v>
       </c>
@@ -39302,7 +39303,7 @@
         <v>-6.6244677121494515</v>
       </c>
     </row>
-    <row r="349" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="63" t="s">
         <v>56</v>
       </c>
@@ -39404,7 +39405,7 @@
         <v>-591.45240000000001</v>
       </c>
     </row>
-    <row r="350" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="63" t="s">
         <v>56</v>
       </c>
@@ -39506,7 +39507,7 @@
         <v>-280.24040000000002</v>
       </c>
     </row>
-    <row r="351" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="63" t="s">
         <v>56</v>
       </c>
@@ -39608,7 +39609,7 @@
         <v>-453.02</v>
       </c>
     </row>
-    <row r="352" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="63" t="s">
         <v>56</v>
       </c>
@@ -39710,7 +39711,7 @@
         <v>-308.27999999999997</v>
       </c>
     </row>
-    <row r="353" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="63" t="s">
         <v>56</v>
       </c>
@@ -39812,7 +39813,7 @@
         <v>-455.06413333333302</v>
       </c>
     </row>
-    <row r="354" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="63" t="s">
         <v>56</v>
       </c>
@@ -39914,7 +39915,7 @@
         <v>-453.02</v>
       </c>
     </row>
-    <row r="355" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="63" t="s">
         <v>56</v>
       </c>
@@ -40016,7 +40017,7 @@
         <v>-177.0692</v>
       </c>
     </row>
-    <row r="356" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="63" t="s">
         <v>56</v>
       </c>
@@ -40118,7 +40119,7 @@
         <v>-137.12453333333301</v>
       </c>
     </row>
-    <row r="357" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="63" t="s">
         <v>56</v>
       </c>
@@ -40220,7 +40221,7 @@
         <v>-455.06413333333302</v>
       </c>
     </row>
-    <row r="358" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="63" t="s">
         <v>56</v>
       </c>
@@ -40322,7 +40323,7 @@
         <v>-453.01666666666699</v>
       </c>
     </row>
-    <row r="359" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="63" t="s">
         <v>56</v>
       </c>
@@ -40424,7 +40425,7 @@
         <v>-392.13386666666702</v>
       </c>
     </row>
-    <row r="360" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="63" t="s">
         <v>56</v>
       </c>
@@ -40526,7 +40527,7 @@
         <v>-591.45240000000001</v>
       </c>
     </row>
-    <row r="361" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="63" t="s">
         <v>56</v>
       </c>
@@ -40628,7 +40629,7 @@
         <v>-308.28160000000003</v>
       </c>
     </row>
-    <row r="362" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="63" t="s">
         <v>56</v>
       </c>
@@ -40730,7 +40731,7 @@
         <v>-317.64333333333298</v>
       </c>
     </row>
-    <row r="363" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="63" t="s">
         <v>56</v>
       </c>
@@ -40832,7 +40833,7 @@
         <v>-2.1369333333333325</v>
       </c>
     </row>
-    <row r="364" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="63" t="s">
         <v>56</v>
       </c>
@@ -40934,7 +40935,7 @@
         <v>-2.1369333333333334</v>
       </c>
     </row>
-    <row r="365" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="63" t="s">
         <v>56</v>
       </c>
@@ -41036,7 +41037,7 @@
         <v>-2.9917066666666665</v>
       </c>
     </row>
-    <row r="366" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="63" t="s">
         <v>56</v>
       </c>
@@ -41138,7 +41139,7 @@
         <v>-6.6244933333333318</v>
       </c>
     </row>
-    <row r="367" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="63" t="s">
         <v>56</v>
       </c>
@@ -41240,7 +41241,7 @@
         <v>-2.9917066666666665</v>
       </c>
     </row>
-    <row r="368" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="63" t="s">
         <v>56</v>
       </c>
@@ -41342,7 +41343,7 @@
         <v>-6.6244933333333327</v>
       </c>
     </row>
-    <row r="369" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="63" t="s">
         <v>56</v>
       </c>
@@ -41444,7 +41445,7 @@
         <v>-6.6244933333333318</v>
       </c>
     </row>
-    <row r="370" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="63" t="s">
         <v>56</v>
       </c>
@@ -41546,7 +41547,7 @@
         <v>-6.6244933333333318</v>
       </c>
     </row>
-    <row r="371" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="97" t="s">
         <v>52</v>
       </c>
@@ -41651,7 +41652,7 @@
         <v>-13.832725703394392</v>
       </c>
     </row>
-    <row r="372" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="97" t="s">
         <v>52</v>
       </c>
@@ -41756,7 +41757,7 @@
         <v>-64.597685224567982</v>
       </c>
     </row>
-    <row r="373" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="97" t="s">
         <v>52</v>
       </c>
@@ -41861,7 +41862,7 @@
         <v>-30.014331962046715</v>
       </c>
     </row>
-    <row r="374" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="97" t="s">
         <v>52</v>
       </c>
@@ -41966,7 +41967,7 @@
         <v>-392.13</v>
       </c>
     </row>
-    <row r="375" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="97" t="s">
         <v>52</v>
       </c>
@@ -42071,7 +42072,7 @@
         <v>-455.06</v>
       </c>
     </row>
-    <row r="376" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="97" t="s">
         <v>52</v>
       </c>
@@ -42176,7 +42177,7 @@
         <v>-392.13</v>
       </c>
     </row>
-    <row r="377" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="97" t="s">
         <v>52</v>
       </c>
@@ -42281,7 +42282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:37" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:37" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="97" t="s">
         <v>52</v>
       </c>
@@ -42387,7 +42388,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK378" xr:uid="{7FE60582-8E84-4795-90E6-91E6C5CD9C07}"/>
+  <autoFilter ref="A1:AK378" xr:uid="{7FE60582-8E84-4795-90E6-91E6C5CD9C07}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="BAU"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -42397,7 +42404,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A30FC1-F5F4-45C0-A8E4-DAC6429A803F}">
   <dimension ref="A1:CU385"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
     <col min="2" max="2" width="40.109375" bestFit="1" customWidth="1"/>
@@ -83494,7 +83501,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
@@ -83573,17 +83580,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="314e7041d7d1561dbe33e80becf1c782">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c838da6aa04a0f137f8b0aba02cfe1" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="613b0908c48a25395136f5b5d1e9264a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5652efc65d8021725ff526b59607fd6" ns2:_="">
     <xsd:import namespace="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -83661,8 +83659,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -83751,6 +83749,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -83758,27 +83765,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8666EB47-972B-4AC1-B919-7FA21786471E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3C6DFED-A995-434B-BD0E-DE6626951453}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBD1A37-C493-4935-BDB3-AA52038BF4AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
